--- a/reports/Debug-purgatory-20260106/For The Day (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260106/For The Day (Prior Year)_Visits.xlsx
@@ -31,19 +31,19 @@
     <t>Location</t>
   </si>
   <si>
+    <t>Purgatory Passes</t>
+  </si>
+  <si>
     <t>Purgatory Comp Tickets</t>
   </si>
   <si>
     <t>Purgatory Uplift Tickets</t>
   </si>
   <si>
+    <t>Purgatory Coaster</t>
+  </si>
+  <si>
     <t>Purgatory Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Passes</t>
-  </si>
-  <si>
-    <t>Purgatory Coaster</t>
   </si>
 </sst>
 </file>
@@ -437,7 +437,7 @@
         <v>45664</v>
       </c>
       <c r="C2" s="2">
-        <v>219</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -451,10 +451,10 @@
         <v>45664</v>
       </c>
       <c r="C3" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -465,10 +465,10 @@
         <v>45664</v>
       </c>
       <c r="C4" s="2">
-        <v>1069</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -479,10 +479,10 @@
         <v>45664</v>
       </c>
       <c r="C5" s="2">
-        <v>751</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -493,10 +493,10 @@
         <v>45664</v>
       </c>
       <c r="C6" s="2">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -507,10 +507,10 @@
         <v>45664</v>
       </c>
       <c r="C7" s="2">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -521,10 +521,10 @@
         <v>45664</v>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>219</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -535,10 +535,10 @@
         <v>45664</v>
       </c>
       <c r="C9" s="2">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -549,10 +549,10 @@
         <v>45664</v>
       </c>
       <c r="C10" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -563,7 +563,7 @@
         <v>45664</v>
       </c>
       <c r="C11" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -577,10 +577,10 @@
         <v>45664</v>
       </c>
       <c r="C12" s="2">
-        <v>5</v>
+        <v>1069</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -591,10 +591,10 @@
         <v>45664</v>
       </c>
       <c r="C13" s="2">
-        <v>9</v>
+        <v>751</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -605,10 +605,10 @@
         <v>45664</v>
       </c>
       <c r="C14" s="2">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
